--- a/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_23.xlsx
+++ b/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_23.xlsx
@@ -664,7 +664,7 @@
     <t>Krstovic</t>
   </si>
   <si>
-    <t>D'aversa</t>
+    <t>D'Aversa</t>
   </si>
   <si>
     <t>Milan</t>
@@ -730,7 +730,7 @@
     <t>Izzo</t>
   </si>
   <si>
-    <t>D'ambrosio</t>
+    <t>D'Ambrosio</t>
   </si>
   <si>
     <t>Pereira P.</t>
